--- a/files/token_usage.xlsx
+++ b/files/token_usage.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -497,9 +497,41 @@
         <v>0.102438</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>28/04/2026</v>
+      </c>
+      <c r="B4" t="str">
+        <v>agent:main:main</v>
+      </c>
+      <c r="C4" t="str">
+        <v>claude-sonnet-4-6 (EU Bedrock)</v>
+      </c>
+      <c r="D4">
+        <v>66</v>
+      </c>
+      <c r="E4">
+        <v>8400</v>
+      </c>
+      <c r="F4">
+        <v>60</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>0.000198</v>
+      </c>
+      <c r="I4">
+        <v>0.126</v>
+      </c>
+      <c r="J4">
+        <v>0.126198</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -517,24 +549,24 @@
       <c r="A2" t="str">
         <v>Giorni monitorati</v>
       </c>
-      <c r="B2" t="str">
-        <v>2</v>
+      <c r="B2">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
         <v>Token IN totali</v>
       </c>
-      <c r="B3" t="str">
-        <v>164</v>
+      <c r="B3">
+        <v>230</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
         <v>Token OUT totali</v>
       </c>
-      <c r="B4" t="str">
-        <v>7800</v>
+      <c r="B4">
+        <v>16200</v>
       </c>
     </row>
     <row r="5">
@@ -542,7 +574,7 @@
         <v>Costo IN totale</v>
       </c>
       <c r="B5" t="str">
-        <v>$0.0005</v>
+        <v>$0.0007</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +582,7 @@
         <v>Costo OUT totale</v>
       </c>
       <c r="B6" t="str">
-        <v>$0.1170</v>
+        <v>$0.2430</v>
       </c>
     </row>
     <row r="7">
@@ -558,23 +590,23 @@
         <v>Costo TOTALE</v>
       </c>
       <c r="B7" t="str">
-        <v>$0.1175</v>
+        <v>$0.2437</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v>Media token IN/day</v>
       </c>
-      <c r="B8" t="str">
-        <v>82</v>
+      <c r="B8">
+        <v>77</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
         <v>Media token OUT/day</v>
       </c>
-      <c r="B9" t="str">
-        <v>3900</v>
+      <c r="B9">
+        <v>5400</v>
       </c>
     </row>
     <row r="10">
@@ -590,7 +622,7 @@
         <v>Ultimo aggiornamento</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
     </row>
   </sheetData>

--- a/files/token_usage.xlsx
+++ b/files/token_usage.xlsx
@@ -1,54 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Log Giornaliero" sheetId="1" r:id="rId1"/>
-    <sheet name="Riepilogo" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log Giornaliero" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Riepilogo" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="2">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="$#,##0.000000"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -66,14 +44,82 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -398,236 +444,346 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Data</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Sessione</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Modello</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Token IN</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Token OUT</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Contesto %</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Compattazioni</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Costo IN ($)</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Costo OUT ($)</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Costo Totale ($)</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Sessione</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Modello</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Token IN</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Token OUT</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Contesto %</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Compattazioni</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Costo IN ($)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Costo OUT ($)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Costo Totale ($)</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>2026-04-27</v>
-      </c>
-      <c r="B2" t="str">
-        <v>agent:main:main</v>
-      </c>
-      <c r="C2" t="str">
-        <v>claude-sonnet-4-6 (EU Bedrock)</v>
-      </c>
-      <c r="D2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>agent:main:main</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6 (EU Bedrock)</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>18</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>1000</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>48</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>2</v>
       </c>
-      <c r="H2">
-        <v>0.000054</v>
-      </c>
-      <c r="I2">
+      <c r="H2" t="n">
+        <v>5.4e-05</v>
+      </c>
+      <c r="I2" t="n">
         <v>0.015</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>0.015054</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>2026-04-27</v>
-      </c>
-      <c r="B3" t="str">
-        <v>agent:main:main</v>
-      </c>
-      <c r="C3" t="str">
-        <v>claude-sonnet-4-6 (EU Bedrock)</v>
-      </c>
-      <c r="D3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>agent:main:main</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6 (EU Bedrock)</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>146</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>6800</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>120</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>3</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>0.000438</v>
       </c>
-      <c r="I3">
+      <c r="I3" t="n">
         <v>0.102</v>
       </c>
-      <c r="J3">
+      <c r="J3" t="n">
         <v>0.102438</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>28/04/2026</v>
-      </c>
-      <c r="B4" t="str">
-        <v>agent:main:main</v>
-      </c>
-      <c r="C4" t="str">
-        <v>claude-sonnet-4-6 (EU Bedrock)</v>
-      </c>
-      <c r="D4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>agent:main:main</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6 (EU Bedrock)</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>66</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>8400</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>60</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>1</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>0.000198</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="n">
         <v>0.126</v>
       </c>
-      <c r="J4">
+      <c r="J4" t="n">
         <v>0.126198</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>agent:main:main</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6 (EU Bedrock)</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F5" t="n">
+        <v>122</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.02403</v>
+      </c>
+    </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v xml:space="preserve"> Riepilogo Token &amp; Costi</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Riepilogo Token &amp; Costi</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>Giorni monitorati</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Giorni monitorati</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>Token IN totali</v>
-      </c>
-      <c r="B3">
-        <v>230</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Token IN totali</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>Token OUT totali</v>
-      </c>
-      <c r="B4">
-        <v>16200</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Token OUT totali</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>17800</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>Costo IN totale</v>
-      </c>
-      <c r="B5" t="str">
-        <v>$0.0007</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Costo IN totale</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>$0.0007</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>Costo OUT totale</v>
-      </c>
-      <c r="B6" t="str">
-        <v>$0.2430</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Costo OUT totale</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>$0.2670</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>Costo TOTALE</v>
-      </c>
-      <c r="B7" t="str">
-        <v>$0.2437</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Costo TOTALE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>$0.2677</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v>Media token IN/day</v>
-      </c>
-      <c r="B8">
-        <v>77</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Media token IN/day</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v>Media token OUT/day</v>
-      </c>
-      <c r="B9">
-        <v>5400</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Media token OUT/day</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4450</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>Modello</v>
-      </c>
-      <c r="B10" t="str">
-        <v>claude-sonnet-4-6 (EU Bedrock)</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Modello</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6 (EU Bedrock)</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v>Ultimo aggiornamento</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-04-28</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ultimo aggiornamento</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>46141</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B11"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/files/token_usage.xlsx
+++ b/files/token_usage.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -652,6 +652,44 @@
       </c>
       <c r="J5" t="n">
         <v>0.02403</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>agent:main:main</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6 (EU Bedrock)</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>26</v>
+      </c>
+      <c r="E6" t="n">
+        <v>823</v>
+      </c>
+      <c r="F6" t="n">
+        <v>55</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>7.8e-05</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.012345</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.012423</v>
       </c>
     </row>
   </sheetData>
@@ -682,7 +720,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -692,7 +730,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>240</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4">
@@ -702,7 +740,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17800</v>
+        <v>18623</v>
       </c>
     </row>
     <row r="5">
@@ -713,7 +751,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$0.0007</t>
+          <t>$0.0008</t>
         </is>
       </c>
     </row>
@@ -725,7 +763,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>$0.2670</t>
+          <t>$0.2793</t>
         </is>
       </c>
     </row>
@@ -737,7 +775,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>$0.2677</t>
+          <t>$0.2801</t>
         </is>
       </c>
     </row>
@@ -748,7 +786,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9">
@@ -758,7 +796,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4450</v>
+        <v>3725</v>
       </c>
     </row>
     <row r="10">
@@ -780,7 +818,7 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
     </row>
   </sheetData>

--- a/files/token_usage.xlsx
+++ b/files/token_usage.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -690,6 +690,44 @@
       </c>
       <c r="J6" t="n">
         <v>0.012423</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>agent:main:main</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6 (EU Bedrock)</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>91</v>
+      </c>
+      <c r="F7" t="n">
+        <v>35</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.001365</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.001395</v>
       </c>
     </row>
   </sheetData>
@@ -720,7 +758,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -730,7 +768,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>266</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4">
@@ -740,7 +778,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18623</v>
+        <v>18714</v>
       </c>
     </row>
     <row r="5">
@@ -763,7 +801,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>$0.2793</t>
+          <t>$0.2807</t>
         </is>
       </c>
     </row>
@@ -775,7 +813,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>$0.2801</t>
+          <t>$0.2815</t>
         </is>
       </c>
     </row>
@@ -786,7 +824,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
@@ -796,7 +834,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3725</v>
+        <v>3119</v>
       </c>
     </row>
     <row r="10">
@@ -817,8 +855,10 @@
           <t>Ultimo aggiornamento</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n">
-        <v>46142</v>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/files/token_usage.xlsx
+++ b/files/token_usage.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -728,6 +728,42 @@
       </c>
       <c r="J7" t="n">
         <v>0.001395</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>agent:main:main</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6 (EU Bedrock)</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>76</v>
+      </c>
+      <c r="F8" t="n">
+        <v>37</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.00114</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.00117</v>
       </c>
     </row>
   </sheetData>
@@ -758,7 +794,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -768,7 +804,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>276</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4">
@@ -778,7 +814,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18714</v>
+        <v>18790</v>
       </c>
     </row>
     <row r="5">
@@ -789,7 +825,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$0.0008</t>
+          <t>$0.000858</t>
         </is>
       </c>
     </row>
@@ -801,7 +837,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>$0.2807</t>
+          <t>$0.2818</t>
         </is>
       </c>
     </row>
@@ -813,7 +849,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>$0.2815</t>
+          <t>$0.2827</t>
         </is>
       </c>
     </row>
@@ -824,7 +860,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
@@ -834,7 +870,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3119</v>
+        <v>2684</v>
       </c>
     </row>
     <row r="10">
@@ -857,7 +893,7 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
